--- a/public/templates/Formulario_Rendicion_Template.xlsx
+++ b/public/templates/Formulario_Rendicion_Template.xlsx
@@ -419,7 +419,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="94">
+  <borders count="95">
     <border>
       <left/>
       <right/>
@@ -1568,11 +1568,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="283">
+  <cellXfs count="285">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -2281,6 +2289,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4875,18 +4885,19 @@
     </row>
     <row r="47" ht="43.5" customHeight="1">
       <c r="A47" s="28" t="n"/>
-      <c r="B47" s="29" t="n"/>
-      <c r="C47" s="29" t="n"/>
-      <c r="D47" s="29" t="n"/>
-      <c r="E47" s="29" t="n"/>
-      <c r="F47" s="29" t="n"/>
+      <c r="B47" s="283" t="n"/>
+      <c r="C47" s="283" t="n"/>
+      <c r="D47" s="283" t="n"/>
+      <c r="E47" s="283" t="n"/>
+      <c r="F47" s="283" t="n"/>
       <c r="G47" s="29" t="n"/>
-      <c r="H47" s="29" t="n"/>
-      <c r="I47" s="29" t="n"/>
-      <c r="J47" s="29" t="n"/>
+      <c r="H47" s="283" t="n"/>
+      <c r="I47" s="283" t="n"/>
+      <c r="J47" s="283" t="n"/>
       <c r="K47" s="29" t="n"/>
-      <c r="L47" s="29" t="n"/>
-      <c r="M47" s="29" t="n"/>
+      <c r="L47" s="283" t="n"/>
+      <c r="M47" s="283" t="n"/>
+      <c r="N47" s="284" t="n"/>
       <c r="Z47" s="12">
         <f>+VLOOKUP(H47,'2. Centros'!J:K,2,0)</f>
         <v/>

--- a/public/templates/Formulario_Rendicion_Template.xlsx
+++ b/public/templates/Formulario_Rendicion_Template.xlsx
@@ -2656,99 +2656,6 @@
     </comment>
   </commentList>
 </comments>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>198121</colOff>
-      <row>0</row>
-      <rowOff>85722</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>998396</colOff>
-      <row>4</row>
-      <rowOff>115244</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Imagen 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="198121" y="85722"/>
-          <a:ext cx="798412" cy="608642"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>205740</colOff>
-      <row>48</row>
-      <rowOff>151447</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>1013592</colOff>
-      <row>52</row>
-      <rowOff>29480</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagen 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="205740" y="10087927"/>
-          <a:ext cx="806983" cy="611500"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6391,7 +6298,6 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="48" min="0" max="12" man="1"/>
   </rowBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/public/templates/Formulario_Rendicion_Template.xlsx
+++ b/public/templates/Formulario_Rendicion_Template.xlsx
@@ -419,7 +419,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="95">
+  <borders count="94">
     <border>
       <left/>
       <right/>
@@ -1568,19 +1568,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="283">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -2289,8 +2281,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4792,19 +4782,18 @@
     </row>
     <row r="47" ht="43.5" customHeight="1">
       <c r="A47" s="28" t="n"/>
-      <c r="B47" s="283" t="n"/>
-      <c r="C47" s="283" t="n"/>
-      <c r="D47" s="283" t="n"/>
-      <c r="E47" s="283" t="n"/>
-      <c r="F47" s="283" t="n"/>
+      <c r="B47" s="29" t="n"/>
+      <c r="C47" s="29" t="n"/>
+      <c r="D47" s="29" t="n"/>
+      <c r="E47" s="29" t="n"/>
+      <c r="F47" s="29" t="n"/>
       <c r="G47" s="29" t="n"/>
-      <c r="H47" s="283" t="n"/>
-      <c r="I47" s="283" t="n"/>
-      <c r="J47" s="283" t="n"/>
+      <c r="H47" s="29" t="n"/>
+      <c r="I47" s="29" t="n"/>
+      <c r="J47" s="29" t="n"/>
       <c r="K47" s="29" t="n"/>
-      <c r="L47" s="283" t="n"/>
-      <c r="M47" s="283" t="n"/>
-      <c r="N47" s="284" t="n"/>
+      <c r="L47" s="29" t="n"/>
+      <c r="M47" s="29" t="n"/>
       <c r="Z47" s="12">
         <f>+VLOOKUP(H47,'2. Centros'!J:K,2,0)</f>
         <v/>
@@ -6298,6 +6287,7 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="48" min="0" max="12" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/public/templates/Formulario_Rendicion_Template.xlsx
+++ b/public/templates/Formulario_Rendicion_Template.xlsx
@@ -2631,21 +2631,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>aclaveria</author>
-  </authors>
-  <commentList>
-    <comment ref="D15" authorId="0" shapeId="0">
-      <text>
-        <t>Nombre de la persona que está rindiendo el fondo, la caja o está solicitando el reembolso de gastos</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/templates/Formulario_Rendicion_Template.xlsx
+++ b/public/templates/Formulario_Rendicion_Template.xlsx
@@ -2631,6 +2631,114 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>aclaveria</author>
+  </authors>
+  <commentList>
+    <comment ref="D15" authorId="0" shapeId="0">
+      <text>
+        <t>Nombre de la persona que está rindiendo el fondo, la caja o está solicitando el reembolso de gastos</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>198121</colOff>
+      <row>0</row>
+      <rowOff>85722</rowOff>
+    </from>
+    <to>
+      <col>0</col>
+      <colOff>998396</colOff>
+      <row>4</row>
+      <rowOff>115244</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Imagen 1"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="198121" y="85722"/>
+          <a:ext cx="798412" cy="608642"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>205740</colOff>
+      <row>48</row>
+      <rowOff>151447</rowOff>
+    </from>
+    <to>
+      <col>0</col>
+      <colOff>1013592</colOff>
+      <row>52</row>
+      <rowOff>29480</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Imagen 1"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="205740" y="10087927"/>
+          <a:ext cx="806983" cy="611500"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/templates/Formulario_Rendicion_Template.xlsx
+++ b/public/templates/Formulario_Rendicion_Template.xlsx
@@ -2631,114 +2631,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>aclaveria</author>
-  </authors>
-  <commentList>
-    <comment ref="D15" authorId="0" shapeId="0">
-      <text>
-        <t>Nombre de la persona que está rindiendo el fondo, la caja o está solicitando el reembolso de gastos</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>198121</colOff>
-      <row>0</row>
-      <rowOff>85722</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>998396</colOff>
-      <row>4</row>
-      <rowOff>115244</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Imagen 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="198121" y="85722"/>
-          <a:ext cx="798412" cy="608642"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>205740</colOff>
-      <row>48</row>
-      <rowOff>151447</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>1013592</colOff>
-      <row>52</row>
-      <rowOff>29480</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagen 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="205740" y="10087927"/>
-          <a:ext cx="806983" cy="611500"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/templates/Formulario_Rendicion_Template.xlsx
+++ b/public/templates/Formulario_Rendicion_Template.xlsx
@@ -2,19 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
-  <workbookProtection lockStructure="1" workbookAlgorithmName="SHA-512" workbookHashValue="5+wHdrGQ4upuya0lh9PYGV4hd5CwnbeswaTUfaBk1ivxrQms0lTk0onzZ/gBuIb5bH4iG+/791pUP+Hz2wqYDw==" workbookSaltValue="WC4lpvm+/oU/L6Mj9TkaHg==" workbookSpinCount="100000"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="641" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formulario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="A1_Empresa">Empresas_[Nombre Empresa]</definedName>
-    <definedName name="A2_Bancos">Listas!$A$2:$A$23</definedName>
-    <definedName name="A3_Documento">Listas!$B$2:$B$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Formulario'!$A$1:$M$101</definedName>
-  </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
